--- a/Data/EXCEL/Transfer/salemon/202206/6492-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6492-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBFF4491-DF3B-4221-B4FD-203719015D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C004A78D-4BFE-496F-8E28-6081DAF0B0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6492-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -1218,21 +1218,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q96"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.75" customWidth="1"/>
-    <col min="2" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="6" width="10.25" customWidth="1"/>
-    <col min="7" max="7" width="11.75" customWidth="1"/>
-    <col min="8" max="8" width="12.25" customWidth="1"/>
-    <col min="9" max="10" width="10.75" customWidth="1"/>
-    <col min="11" max="11" width="12.25" customWidth="1"/>
-    <col min="12" max="12" width="10.75" customWidth="1"/>
-    <col min="13" max="13" width="12.25" customWidth="1"/>
-    <col min="14" max="15" width="10.75" customWidth="1"/>
-    <col min="16" max="16" width="12.25" customWidth="1"/>
-    <col min="17" max="17" width="12" customWidth="1"/>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="5" width="11.75" customWidth="1"/>
+    <col min="6" max="6" width="11.25" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="10" width="11.75" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="11.75" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="15" width="11.75" customWidth="1"/>
+    <col min="16" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,25 +1385,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>91.7</v>
+        <v>79.2</v>
       </c>
       <c r="C5" s="7">
-        <v>79.5</v>
+        <v>69.599999999999994</v>
       </c>
       <c r="D5" s="7">
-        <v>92</v>
+        <v>82.9</v>
       </c>
       <c r="E5" s="7">
-        <v>75</v>
+        <v>69.5</v>
       </c>
       <c r="F5" s="8">
-        <v>-12.2</v>
+        <v>-9.9</v>
       </c>
       <c r="G5" s="8">
-        <v>-13.3</v>
+        <v>-12.45</v>
       </c>
       <c r="H5" s="9">
         <v>8.0000000000000004E-4</v>
@@ -1415,10 +1415,10 @@
         <v>66</v>
       </c>
       <c r="K5" s="9">
-        <v>4.1999999999999997E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="L5" s="10">
-        <v>66.400000000000006</v>
+        <v>66.7</v>
       </c>
       <c r="M5" s="9">
         <v>8.0000000000000004E-4</v>
@@ -1430,33 +1430,33 @@
         <v>66</v>
       </c>
       <c r="P5" s="9">
-        <v>4.1999999999999997E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q5" s="10">
-        <v>66.400000000000006</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>78.400000000000006</v>
+        <v>91.7</v>
       </c>
       <c r="C6" s="7">
-        <v>91.7</v>
+        <v>79.5</v>
       </c>
       <c r="D6" s="7">
-        <v>115.5</v>
+        <v>92</v>
       </c>
       <c r="E6" s="7">
-        <v>77</v>
-      </c>
-      <c r="F6" s="10">
-        <v>13.3</v>
-      </c>
-      <c r="G6" s="10">
-        <v>16.96</v>
+        <v>75</v>
+      </c>
+      <c r="F6" s="8">
+        <v>-12.2</v>
+      </c>
+      <c r="G6" s="8">
+        <v>-13.3</v>
       </c>
       <c r="H6" s="9">
         <v>8.0000000000000004E-4</v>
@@ -1468,10 +1468,10 @@
         <v>66</v>
       </c>
       <c r="K6" s="9">
-        <v>3.3E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="L6" s="10">
-        <v>66.5</v>
+        <v>66.400000000000006</v>
       </c>
       <c r="M6" s="9">
         <v>8.0000000000000004E-4</v>
@@ -1483,298 +1483,298 @@
         <v>66</v>
       </c>
       <c r="P6" s="9">
-        <v>3.3E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="Q6" s="10">
-        <v>66.5</v>
+        <v>66.400000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>90.5</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="C7" s="7">
-        <v>78.400000000000006</v>
+        <v>91.7</v>
       </c>
       <c r="D7" s="7">
-        <v>94</v>
+        <v>115.5</v>
       </c>
       <c r="E7" s="7">
-        <v>74</v>
-      </c>
-      <c r="F7" s="8">
-        <v>-10.7</v>
-      </c>
-      <c r="G7" s="8">
-        <v>-12.01</v>
+        <v>77</v>
+      </c>
+      <c r="F7" s="10">
+        <v>13.3</v>
+      </c>
+      <c r="G7" s="10">
+        <v>16.96</v>
       </c>
       <c r="H7" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="I7" s="8">
-        <v>-1.19</v>
+      <c r="I7" s="9">
+        <v>0</v>
       </c>
       <c r="J7" s="10">
         <v>66</v>
       </c>
       <c r="K7" s="9">
-        <v>2.5000000000000001E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="L7" s="10">
-        <v>66.7</v>
+        <v>66.5</v>
       </c>
       <c r="M7" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="N7" s="8">
-        <v>-1.19</v>
+      <c r="N7" s="9">
+        <v>0</v>
       </c>
       <c r="O7" s="10">
         <v>66</v>
       </c>
       <c r="P7" s="9">
-        <v>2.5000000000000001E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="Q7" s="10">
-        <v>66.7</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>102</v>
+        <v>90.5</v>
       </c>
       <c r="C8" s="7">
-        <v>89.1</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="D8" s="7">
-        <v>102.5</v>
+        <v>94</v>
       </c>
       <c r="E8" s="7">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="F8" s="8">
-        <v>-12.4</v>
+        <v>-10.7</v>
       </c>
       <c r="G8" s="8">
-        <v>-12.22</v>
+        <v>-12.01</v>
       </c>
       <c r="H8" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="I8" s="10">
-        <v>1.2</v>
+      <c r="I8" s="8">
+        <v>-1.19</v>
       </c>
       <c r="J8" s="10">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K8" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="L8" s="10">
-        <v>67</v>
+        <v>66.7</v>
       </c>
       <c r="M8" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="N8" s="10">
-        <v>1.2</v>
+      <c r="N8" s="8">
+        <v>-1.19</v>
       </c>
       <c r="O8" s="10">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="P8" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="Q8" s="10">
-        <v>67</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C9" s="7">
-        <v>101.5</v>
+        <v>89.1</v>
       </c>
       <c r="D9" s="7">
-        <v>112</v>
+        <v>102.5</v>
       </c>
       <c r="E9" s="7">
-        <v>96.5</v>
+        <v>88</v>
       </c>
       <c r="F9" s="8">
-        <v>-2.5</v>
+        <v>-12.4</v>
       </c>
       <c r="G9" s="8">
-        <v>-2.4</v>
+        <v>-12.22</v>
       </c>
       <c r="H9" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>17</v>
+      <c r="I9" s="10">
+        <v>1.2</v>
       </c>
       <c r="J9" s="10">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K9" s="9">
-        <v>8.0000000000000004E-4</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="L9" s="10">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M9" s="9">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="N9" s="9" t="s">
-        <v>17</v>
+      <c r="N9" s="10">
+        <v>1.2</v>
       </c>
       <c r="O9" s="10">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P9" s="9">
-        <v>8.0000000000000004E-4</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="Q9" s="10">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>90.9</v>
+        <v>105</v>
       </c>
       <c r="C10" s="7">
-        <v>104</v>
+        <v>101.5</v>
       </c>
       <c r="D10" s="7">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="E10" s="7">
-        <v>88.5</v>
-      </c>
-      <c r="F10" s="10">
-        <v>14.2</v>
-      </c>
-      <c r="G10" s="10">
-        <v>15.81</v>
+        <v>96.5</v>
+      </c>
+      <c r="F10" s="8">
+        <v>-2.5</v>
+      </c>
+      <c r="G10" s="8">
+        <v>-2.4</v>
       </c>
       <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8">
-        <v>-100</v>
-      </c>
-      <c r="J10" s="8">
-        <v>-100</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="10">
+        <v>66</v>
       </c>
       <c r="K10" s="9">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="L10" s="8">
-        <v>-10.8</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="L10" s="10">
+        <v>66</v>
       </c>
       <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="8">
-        <v>-100</v>
-      </c>
-      <c r="O10" s="8">
-        <v>-100</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O10" s="10">
+        <v>66</v>
       </c>
       <c r="P10" s="9">
-        <v>5.4999999999999997E-3</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>-10.8</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>124</v>
+        <v>90.9</v>
       </c>
       <c r="C11" s="7">
-        <v>89.8</v>
+        <v>104</v>
       </c>
       <c r="D11" s="7">
-        <v>125.5</v>
+        <v>134</v>
       </c>
       <c r="E11" s="7">
-        <v>83</v>
-      </c>
-      <c r="F11" s="8">
-        <v>-35.700000000000003</v>
-      </c>
-      <c r="G11" s="8">
-        <v>-28.45</v>
+        <v>88.5</v>
+      </c>
+      <c r="F11" s="10">
+        <v>14.2</v>
+      </c>
+      <c r="G11" s="10">
+        <v>15.81</v>
       </c>
       <c r="H11" s="9">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="I11" s="9">
-        <v>0</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>-100</v>
+      </c>
+      <c r="J11" s="8">
+        <v>-100</v>
       </c>
       <c r="K11" s="9">
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="L11" s="8">
-        <v>-2.99</v>
+        <v>-10.8</v>
       </c>
       <c r="M11" s="9">
-        <v>5.0000000000000001E-4</v>
-      </c>
-      <c r="N11" s="9">
-        <v>0</v>
-      </c>
-      <c r="O11" s="9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>-100</v>
+      </c>
+      <c r="O11" s="8">
+        <v>-100</v>
       </c>
       <c r="P11" s="9">
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q11" s="8">
-        <v>-2.99</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="C12" s="7">
+        <v>89.8</v>
+      </c>
+      <c r="D12" s="7">
         <v>125.5</v>
       </c>
-      <c r="D12" s="7">
-        <v>149.5</v>
-      </c>
       <c r="E12" s="7">
-        <v>115.5</v>
+        <v>83</v>
       </c>
       <c r="F12" s="8">
-        <v>-21</v>
+        <v>-35.700000000000003</v>
       </c>
       <c r="G12" s="8">
-        <v>-14.33</v>
+        <v>-28.45</v>
       </c>
       <c r="H12" s="9">
         <v>5.0000000000000001E-4</v>
@@ -1786,10 +1786,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="9">
-        <v>5.0000000000000001E-3</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="L12" s="8">
-        <v>-3.28</v>
+        <v>-2.99</v>
       </c>
       <c r="M12" s="9">
         <v>5.0000000000000001E-4</v>
@@ -1801,33 +1801,33 @@
         <v>0</v>
       </c>
       <c r="P12" s="9">
-        <v>5.0000000000000001E-3</v>
+        <v>5.4999999999999997E-3</v>
       </c>
       <c r="Q12" s="8">
-        <v>-3.28</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="C13" s="7">
-        <v>146.5</v>
+        <v>125.5</v>
       </c>
       <c r="D13" s="7">
-        <v>169</v>
+        <v>149.5</v>
       </c>
       <c r="E13" s="7">
-        <v>138</v>
+        <v>115.5</v>
       </c>
       <c r="F13" s="8">
-        <v>-2.5</v>
+        <v>-21</v>
       </c>
       <c r="G13" s="8">
-        <v>-1.68</v>
+        <v>-14.33</v>
       </c>
       <c r="H13" s="9">
         <v>5.0000000000000001E-4</v>
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="K13" s="9">
-        <v>4.4999999999999997E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="L13" s="8">
-        <v>-3.64</v>
+        <v>-3.28</v>
       </c>
       <c r="M13" s="9">
         <v>5.0000000000000001E-4</v>
@@ -1854,33 +1854,33 @@
         <v>0</v>
       </c>
       <c r="P13" s="9">
-        <v>4.4999999999999997E-3</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q13" s="8">
-        <v>-3.64</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>124</v>
+        <v>160</v>
       </c>
       <c r="C14" s="7">
-        <v>149</v>
+        <v>146.5</v>
       </c>
       <c r="D14" s="7">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E14" s="7">
-        <v>120</v>
-      </c>
-      <c r="F14" s="10">
-        <v>25.5</v>
-      </c>
-      <c r="G14" s="10">
-        <v>20.65</v>
+        <v>138</v>
+      </c>
+      <c r="F14" s="8">
+        <v>-2.5</v>
+      </c>
+      <c r="G14" s="8">
+        <v>-1.68</v>
       </c>
       <c r="H14" s="9">
         <v>5.0000000000000001E-4</v>
@@ -1892,10 +1892,10 @@
         <v>0</v>
       </c>
       <c r="K14" s="9">
-        <v>4.0000000000000001E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="L14" s="8">
-        <v>-4.07</v>
+        <v>-3.64</v>
       </c>
       <c r="M14" s="9">
         <v>5.0000000000000001E-4</v>
@@ -1907,33 +1907,33 @@
         <v>0</v>
       </c>
       <c r="P14" s="9">
-        <v>4.0000000000000001E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="Q14" s="8">
-        <v>-4.07</v>
+        <v>-3.64</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>178</v>
+        <v>124</v>
       </c>
       <c r="C15" s="7">
-        <v>123.5</v>
+        <v>149</v>
       </c>
       <c r="D15" s="7">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="E15" s="7">
-        <v>122.5</v>
-      </c>
-      <c r="F15" s="8">
-        <v>-55</v>
-      </c>
-      <c r="G15" s="8">
-        <v>-30.81</v>
+        <v>120</v>
+      </c>
+      <c r="F15" s="10">
+        <v>25.5</v>
+      </c>
+      <c r="G15" s="10">
+        <v>20.65</v>
       </c>
       <c r="H15" s="9">
         <v>5.0000000000000001E-4</v>
@@ -1945,10 +1945,10 @@
         <v>0</v>
       </c>
       <c r="K15" s="9">
-        <v>3.5000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="L15" s="8">
-        <v>-4.63</v>
+        <v>-4.07</v>
       </c>
       <c r="M15" s="9">
         <v>5.0000000000000001E-4</v>
@@ -1960,33 +1960,33 @@
         <v>0</v>
       </c>
       <c r="P15" s="9">
-        <v>3.5000000000000001E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="Q15" s="8">
-        <v>-4.63</v>
+        <v>-4.07</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>172.5</v>
+        <v>178</v>
       </c>
       <c r="C16" s="7">
-        <v>178.5</v>
+        <v>123.5</v>
       </c>
       <c r="D16" s="7">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="E16" s="7">
-        <v>166.5</v>
-      </c>
-      <c r="F16" s="10">
-        <v>21.5</v>
-      </c>
-      <c r="G16" s="10">
-        <v>13.69</v>
+        <v>122.5</v>
+      </c>
+      <c r="F16" s="8">
+        <v>-55</v>
+      </c>
+      <c r="G16" s="8">
+        <v>-30.81</v>
       </c>
       <c r="H16" s="9">
         <v>5.0000000000000001E-4</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="9">
-        <v>3.0000000000000001E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="L16" s="8">
-        <v>-5.36</v>
+        <v>-4.63</v>
       </c>
       <c r="M16" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2013,33 +2013,33 @@
         <v>0</v>
       </c>
       <c r="P16" s="9">
-        <v>3.0000000000000001E-3</v>
+        <v>3.5000000000000001E-3</v>
       </c>
       <c r="Q16" s="8">
-        <v>-5.36</v>
+        <v>-4.63</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>156</v>
+        <v>172.5</v>
       </c>
       <c r="C17" s="7">
-        <v>157</v>
+        <v>178.5</v>
       </c>
       <c r="D17" s="7">
-        <v>173.5</v>
+        <v>206</v>
       </c>
       <c r="E17" s="7">
-        <v>122.5</v>
+        <v>166.5</v>
       </c>
       <c r="F17" s="10">
-        <v>3</v>
+        <v>21.5</v>
       </c>
       <c r="G17" s="10">
-        <v>1.95</v>
+        <v>13.69</v>
       </c>
       <c r="H17" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2051,10 +2051,10 @@
         <v>0</v>
       </c>
       <c r="K17" s="9">
-        <v>2.5000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="L17" s="8">
-        <v>-6.36</v>
+        <v>-5.36</v>
       </c>
       <c r="M17" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2066,33 +2066,33 @@
         <v>0</v>
       </c>
       <c r="P17" s="9">
-        <v>2.5000000000000001E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q17" s="8">
-        <v>-6.36</v>
+        <v>-5.36</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="C18" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D18" s="7">
-        <v>176.5</v>
+        <v>173.5</v>
       </c>
       <c r="E18" s="7">
-        <v>151</v>
-      </c>
-      <c r="F18" s="8">
-        <v>-21</v>
-      </c>
-      <c r="G18" s="8">
-        <v>-12</v>
+        <v>122.5</v>
+      </c>
+      <c r="F18" s="10">
+        <v>3</v>
+      </c>
+      <c r="G18" s="10">
+        <v>1.95</v>
       </c>
       <c r="H18" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2104,10 +2104,10 @@
         <v>0</v>
       </c>
       <c r="K18" s="9">
-        <v>2E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="L18" s="8">
-        <v>-7.83</v>
+        <v>-6.36</v>
       </c>
       <c r="M18" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2119,33 +2119,33 @@
         <v>0</v>
       </c>
       <c r="P18" s="9">
-        <v>2E-3</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="Q18" s="8">
-        <v>-7.83</v>
+        <v>-6.36</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>181.5</v>
+        <v>175</v>
       </c>
       <c r="C19" s="7">
-        <v>175</v>
+        <v>154</v>
       </c>
       <c r="D19" s="7">
-        <v>187.5</v>
+        <v>176.5</v>
       </c>
       <c r="E19" s="7">
-        <v>146.5</v>
+        <v>151</v>
       </c>
       <c r="F19" s="8">
-        <v>-2</v>
+        <v>-21</v>
       </c>
       <c r="G19" s="8">
-        <v>-1.1299999999999999</v>
+        <v>-12</v>
       </c>
       <c r="H19" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2157,10 +2157,10 @@
         <v>0</v>
       </c>
       <c r="K19" s="9">
-        <v>1.5E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="L19" s="8">
-        <v>-10.199999999999999</v>
+        <v>-7.83</v>
       </c>
       <c r="M19" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2172,33 +2172,33 @@
         <v>0</v>
       </c>
       <c r="P19" s="9">
-        <v>1.5E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="Q19" s="8">
-        <v>-10.199999999999999</v>
+        <v>-7.83</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>170</v>
+        <v>181.5</v>
       </c>
       <c r="C20" s="7">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D20" s="7">
-        <v>205</v>
+        <v>187.5</v>
       </c>
       <c r="E20" s="7">
-        <v>170</v>
-      </c>
-      <c r="F20" s="10">
-        <v>7</v>
-      </c>
-      <c r="G20" s="10">
-        <v>4.12</v>
+        <v>146.5</v>
+      </c>
+      <c r="F20" s="8">
+        <v>-2</v>
+      </c>
+      <c r="G20" s="8">
+        <v>-1.1299999999999999</v>
       </c>
       <c r="H20" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2210,10 +2210,10 @@
         <v>0</v>
       </c>
       <c r="K20" s="9">
-        <v>1E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="L20" s="8">
-        <v>-14.5</v>
+        <v>-10.199999999999999</v>
       </c>
       <c r="M20" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2225,33 +2225,33 @@
         <v>0</v>
       </c>
       <c r="P20" s="9">
-        <v>1E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q20" s="8">
-        <v>-14.5</v>
+        <v>-10.199999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
-        <v>227</v>
+        <v>170</v>
       </c>
       <c r="C21" s="7">
+        <v>177</v>
+      </c>
+      <c r="D21" s="7">
+        <v>205</v>
+      </c>
+      <c r="E21" s="7">
         <v>170</v>
       </c>
-      <c r="D21" s="7">
-        <v>227</v>
-      </c>
-      <c r="E21" s="7">
-        <v>158.5</v>
-      </c>
-      <c r="F21" s="8">
-        <v>-55</v>
-      </c>
-      <c r="G21" s="8">
-        <v>-24.44</v>
+      <c r="F21" s="10">
+        <v>7</v>
+      </c>
+      <c r="G21" s="10">
+        <v>4.12</v>
       </c>
       <c r="H21" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2259,14 +2259,14 @@
       <c r="I21" s="9">
         <v>0</v>
       </c>
-      <c r="J21" s="8">
-        <v>-25.4</v>
+      <c r="J21" s="9">
+        <v>0</v>
       </c>
       <c r="K21" s="9">
-        <v>5.0000000000000001E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="L21" s="8">
-        <v>-25.4</v>
+        <v>-14.5</v>
       </c>
       <c r="M21" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2274,37 +2274,37 @@
       <c r="N21" s="9">
         <v>0</v>
       </c>
-      <c r="O21" s="8">
-        <v>-25.4</v>
+      <c r="O21" s="9">
+        <v>0</v>
       </c>
       <c r="P21" s="9">
-        <v>5.0000000000000001E-4</v>
+        <v>1E-3</v>
       </c>
       <c r="Q21" s="8">
-        <v>-25.4</v>
+        <v>-14.5</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C22" s="7">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="D22" s="7">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="E22" s="7">
-        <v>208</v>
-      </c>
-      <c r="F22" s="10">
-        <v>7</v>
-      </c>
-      <c r="G22" s="10">
-        <v>3.21</v>
+        <v>158.5</v>
+      </c>
+      <c r="F22" s="8">
+        <v>-55</v>
+      </c>
+      <c r="G22" s="8">
+        <v>-24.44</v>
       </c>
       <c r="H22" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2316,10 +2316,10 @@
         <v>-25.4</v>
       </c>
       <c r="K22" s="9">
-        <v>6.1999999999999998E-3</v>
-      </c>
-      <c r="L22" s="10">
-        <v>105.7</v>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="L22" s="8">
+        <v>-25.4</v>
       </c>
       <c r="M22" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2331,33 +2331,33 @@
         <v>-25.4</v>
       </c>
       <c r="P22" s="9">
-        <v>6.1999999999999998E-3</v>
-      </c>
-      <c r="Q22" s="10">
-        <v>105.7</v>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>-25.4</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>235.5</v>
+        <v>220</v>
       </c>
       <c r="C23" s="7">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D23" s="7">
-        <v>270</v>
+        <v>239</v>
       </c>
       <c r="E23" s="7">
-        <v>201.5</v>
-      </c>
-      <c r="F23" s="8">
-        <v>-10.5</v>
-      </c>
-      <c r="G23" s="8">
-        <v>-4.5999999999999996</v>
+        <v>208</v>
+      </c>
+      <c r="F23" s="10">
+        <v>7</v>
+      </c>
+      <c r="G23" s="10">
+        <v>3.21</v>
       </c>
       <c r="H23" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2365,14 +2365,14 @@
       <c r="I23" s="9">
         <v>0</v>
       </c>
-      <c r="J23" s="10">
-        <v>194.1</v>
+      <c r="J23" s="8">
+        <v>-25.4</v>
       </c>
       <c r="K23" s="9">
-        <v>5.7000000000000002E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="L23" s="10">
-        <v>143.30000000000001</v>
+        <v>105.7</v>
       </c>
       <c r="M23" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2380,37 +2380,37 @@
       <c r="N23" s="9">
         <v>0</v>
       </c>
-      <c r="O23" s="10">
-        <v>194.1</v>
+      <c r="O23" s="8">
+        <v>-25.4</v>
       </c>
       <c r="P23" s="9">
-        <v>5.7000000000000002E-3</v>
+        <v>6.1999999999999998E-3</v>
       </c>
       <c r="Q23" s="10">
-        <v>143.30000000000001</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>263</v>
+        <v>235.5</v>
       </c>
       <c r="C24" s="7">
-        <v>228.5</v>
+        <v>218</v>
       </c>
       <c r="D24" s="7">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="E24" s="7">
-        <v>180</v>
+        <v>201.5</v>
       </c>
       <c r="F24" s="8">
-        <v>-42</v>
+        <v>-10.5</v>
       </c>
       <c r="G24" s="8">
-        <v>-15.53</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="H24" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2422,10 +2422,10 @@
         <v>194.1</v>
       </c>
       <c r="K24" s="9">
-        <v>5.1999999999999998E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="L24" s="10">
-        <v>138.19999999999999</v>
+        <v>143.30000000000001</v>
       </c>
       <c r="M24" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2437,33 +2437,33 @@
         <v>194.1</v>
       </c>
       <c r="P24" s="9">
-        <v>5.1999999999999998E-3</v>
+        <v>5.7000000000000002E-3</v>
       </c>
       <c r="Q24" s="10">
-        <v>138.19999999999999</v>
+        <v>143.30000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="C25" s="7">
-        <v>270.5</v>
+        <v>228.5</v>
       </c>
       <c r="D25" s="7">
-        <v>309.5</v>
+        <v>282</v>
       </c>
       <c r="E25" s="7">
-        <v>166</v>
-      </c>
-      <c r="F25" s="10">
-        <v>98</v>
-      </c>
-      <c r="G25" s="10">
-        <v>56.81</v>
+        <v>180</v>
+      </c>
+      <c r="F25" s="8">
+        <v>-42</v>
+      </c>
+      <c r="G25" s="8">
+        <v>-15.53</v>
       </c>
       <c r="H25" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2475,10 +2475,10 @@
         <v>194.1</v>
       </c>
       <c r="K25" s="9">
-        <v>4.7000000000000002E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="L25" s="10">
-        <v>133.5</v>
+        <v>138.19999999999999</v>
       </c>
       <c r="M25" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2490,33 +2490,33 @@
         <v>194.1</v>
       </c>
       <c r="P25" s="9">
-        <v>4.7000000000000002E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
       <c r="Q25" s="10">
-        <v>133.5</v>
+        <v>138.19999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="C26" s="7">
-        <v>172.5</v>
+        <v>270.5</v>
       </c>
       <c r="D26" s="7">
-        <v>197</v>
+        <v>309.5</v>
       </c>
       <c r="E26" s="7">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="F26" s="10">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="G26" s="10">
-        <v>27.31</v>
+        <v>56.81</v>
       </c>
       <c r="H26" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2528,10 +2528,10 @@
         <v>194.1</v>
       </c>
       <c r="K26" s="9">
-        <v>4.1999999999999997E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="L26" s="10">
-        <v>127.9</v>
+        <v>133.5</v>
       </c>
       <c r="M26" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2543,33 +2543,33 @@
         <v>194.1</v>
       </c>
       <c r="P26" s="9">
-        <v>4.1999999999999997E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="Q26" s="10">
-        <v>127.9</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C27" s="7">
-        <v>135.5</v>
+        <v>172.5</v>
       </c>
       <c r="D27" s="7">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="E27" s="7">
-        <v>119</v>
-      </c>
-      <c r="F27" s="8">
-        <v>-4</v>
-      </c>
-      <c r="G27" s="8">
-        <v>-2.87</v>
+        <v>136</v>
+      </c>
+      <c r="F27" s="10">
+        <v>37</v>
+      </c>
+      <c r="G27" s="10">
+        <v>27.31</v>
       </c>
       <c r="H27" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2581,10 +2581,10 @@
         <v>194.1</v>
       </c>
       <c r="K27" s="9">
-        <v>3.7000000000000002E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="L27" s="10">
-        <v>119.8</v>
+        <v>127.9</v>
       </c>
       <c r="M27" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2596,33 +2596,33 @@
         <v>194.1</v>
       </c>
       <c r="P27" s="9">
-        <v>3.7000000000000002E-3</v>
+        <v>4.1999999999999997E-3</v>
       </c>
       <c r="Q27" s="10">
-        <v>119.8</v>
+        <v>127.9</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>126.5</v>
+        <v>140</v>
       </c>
       <c r="C28" s="7">
-        <v>139.5</v>
+        <v>135.5</v>
       </c>
       <c r="D28" s="7">
-        <v>139.5</v>
+        <v>187</v>
       </c>
       <c r="E28" s="7">
-        <v>105</v>
-      </c>
-      <c r="F28" s="10">
-        <v>13</v>
-      </c>
-      <c r="G28" s="10">
-        <v>10.28</v>
+        <v>119</v>
+      </c>
+      <c r="F28" s="8">
+        <v>-4</v>
+      </c>
+      <c r="G28" s="8">
+        <v>-2.87</v>
       </c>
       <c r="H28" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2634,10 +2634,10 @@
         <v>194.1</v>
       </c>
       <c r="K28" s="9">
-        <v>3.2000000000000002E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="L28" s="10">
-        <v>111.3</v>
+        <v>119.8</v>
       </c>
       <c r="M28" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2649,33 +2649,33 @@
         <v>194.1</v>
       </c>
       <c r="P28" s="9">
-        <v>3.2000000000000002E-3</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="Q28" s="10">
-        <v>111.3</v>
+        <v>119.8</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>77</v>
+        <v>126.5</v>
       </c>
       <c r="C29" s="7">
-        <v>126.5</v>
+        <v>139.5</v>
       </c>
       <c r="D29" s="7">
-        <v>143.5</v>
+        <v>139.5</v>
       </c>
       <c r="E29" s="7">
-        <v>75.5</v>
+        <v>105</v>
       </c>
       <c r="F29" s="10">
-        <v>47.4</v>
+        <v>13</v>
       </c>
       <c r="G29" s="10">
-        <v>59.92</v>
+        <v>10.28</v>
       </c>
       <c r="H29" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2687,10 +2687,10 @@
         <v>194.1</v>
       </c>
       <c r="K29" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="L29" s="10">
-        <v>99.2</v>
+        <v>111.3</v>
       </c>
       <c r="M29" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2702,33 +2702,33 @@
         <v>194.1</v>
       </c>
       <c r="P29" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="Q29" s="10">
-        <v>99.2</v>
+        <v>111.3</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>59.7</v>
+        <v>77</v>
       </c>
       <c r="C30" s="7">
-        <v>79.099999999999994</v>
+        <v>126.5</v>
       </c>
       <c r="D30" s="7">
-        <v>84.6</v>
+        <v>143.5</v>
       </c>
       <c r="E30" s="7">
-        <v>53.6</v>
+        <v>75.5</v>
       </c>
       <c r="F30" s="10">
-        <v>24.8</v>
+        <v>47.4</v>
       </c>
       <c r="G30" s="10">
-        <v>45.67</v>
+        <v>59.92</v>
       </c>
       <c r="H30" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2740,10 +2740,10 @@
         <v>194.1</v>
       </c>
       <c r="K30" s="9">
-        <v>2.2000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="L30" s="10">
-        <v>85.5</v>
+        <v>99.2</v>
       </c>
       <c r="M30" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2755,33 +2755,33 @@
         <v>194.1</v>
       </c>
       <c r="P30" s="9">
-        <v>2.2000000000000001E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="Q30" s="10">
-        <v>85.5</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>63</v>
+        <v>59.7</v>
       </c>
       <c r="C31" s="7">
-        <v>54.3</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="D31" s="7">
-        <v>64.099999999999994</v>
+        <v>84.6</v>
       </c>
       <c r="E31" s="7">
-        <v>40.5</v>
-      </c>
-      <c r="F31" s="8">
-        <v>-9</v>
-      </c>
-      <c r="G31" s="8">
-        <v>-14.22</v>
+        <v>53.6</v>
+      </c>
+      <c r="F31" s="10">
+        <v>24.8</v>
+      </c>
+      <c r="G31" s="10">
+        <v>45.67</v>
       </c>
       <c r="H31" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2793,10 +2793,10 @@
         <v>194.1</v>
       </c>
       <c r="K31" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="L31" s="10">
-        <v>67</v>
+        <v>85.5</v>
       </c>
       <c r="M31" s="9">
         <v>5.0000000000000001E-4</v>
@@ -2808,245 +2808,245 @@
         <v>194.1</v>
       </c>
       <c r="P31" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="Q31" s="10">
-        <v>67</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>62.8</v>
+        <v>63</v>
       </c>
       <c r="C32" s="7">
-        <v>63.3</v>
+        <v>54.3</v>
       </c>
       <c r="D32" s="7">
-        <v>66.3</v>
+        <v>64.099999999999994</v>
       </c>
       <c r="E32" s="7">
-        <v>61.7</v>
-      </c>
-      <c r="F32" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="G32" s="10">
-        <v>1.28</v>
+        <v>40.5</v>
+      </c>
+      <c r="F32" s="8">
+        <v>-9</v>
+      </c>
+      <c r="G32" s="8">
+        <v>-14.22</v>
       </c>
       <c r="H32" s="9">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="I32" s="8">
-        <v>-25.4</v>
+      <c r="I32" s="9">
+        <v>0</v>
       </c>
       <c r="J32" s="10">
         <v>194.1</v>
       </c>
       <c r="K32" s="9">
-        <v>1.1999999999999999E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="L32" s="10">
-        <v>39.299999999999997</v>
+        <v>67</v>
       </c>
       <c r="M32" s="9">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="N32" s="8">
-        <v>-25.4</v>
+      <c r="N32" s="9">
+        <v>0</v>
       </c>
       <c r="O32" s="10">
         <v>194.1</v>
       </c>
       <c r="P32" s="9">
-        <v>1.1999999999999999E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="Q32" s="10">
-        <v>39.299999999999997</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>63.8</v>
+        <v>62.8</v>
       </c>
       <c r="C33" s="7">
-        <v>62.5</v>
+        <v>63.3</v>
       </c>
       <c r="D33" s="7">
-        <v>64.3</v>
+        <v>66.3</v>
       </c>
       <c r="E33" s="7">
-        <v>61.1</v>
-      </c>
-      <c r="F33" s="8">
-        <v>-2</v>
-      </c>
-      <c r="G33" s="8">
-        <v>-3.1</v>
+        <v>61.7</v>
+      </c>
+      <c r="F33" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="G33" s="10">
+        <v>1.28</v>
       </c>
       <c r="H33" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="I33" s="9">
-        <v>0</v>
-      </c>
-      <c r="J33" s="9">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="I33" s="8">
+        <v>-25.4</v>
+      </c>
+      <c r="J33" s="10">
+        <v>194.1</v>
       </c>
       <c r="K33" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="L33" s="9">
-        <v>0</v>
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="L33" s="10">
+        <v>39.299999999999997</v>
       </c>
       <c r="M33" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="N33" s="9">
-        <v>0</v>
-      </c>
-      <c r="O33" s="9">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="N33" s="8">
+        <v>-25.4</v>
+      </c>
+      <c r="O33" s="10">
+        <v>194.1</v>
       </c>
       <c r="P33" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q33" s="9">
-        <v>0</v>
+        <v>1.1999999999999999E-3</v>
+      </c>
+      <c r="Q33" s="10">
+        <v>39.299999999999997</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>62.6</v>
+        <v>63.8</v>
       </c>
       <c r="C34" s="7">
-        <v>64.5</v>
+        <v>62.5</v>
       </c>
       <c r="D34" s="7">
-        <v>66.599999999999994</v>
+        <v>64.3</v>
       </c>
       <c r="E34" s="7">
-        <v>62.3</v>
-      </c>
-      <c r="F34" s="10">
-        <v>0.8</v>
-      </c>
-      <c r="G34" s="10">
-        <v>1.26</v>
+        <v>61.1</v>
+      </c>
+      <c r="F34" s="8">
+        <v>-2</v>
+      </c>
+      <c r="G34" s="8">
+        <v>-3.1</v>
       </c>
       <c r="H34" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I34" s="10">
-        <v>294.10000000000002</v>
-      </c>
-      <c r="J34" s="10">
-        <v>1.51</v>
+      <c r="I34" s="9">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9">
+        <v>0</v>
       </c>
       <c r="K34" s="9">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="L34" s="8">
-        <v>-59.1</v>
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="L34" s="9">
+        <v>0</v>
       </c>
       <c r="M34" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="N34" s="10">
-        <v>294.10000000000002</v>
-      </c>
-      <c r="O34" s="10">
-        <v>1.51</v>
+      <c r="N34" s="9">
+        <v>0</v>
+      </c>
+      <c r="O34" s="9">
+        <v>0</v>
       </c>
       <c r="P34" s="9">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="Q34" s="8">
-        <v>-59.1</v>
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7">
-        <v>65.099999999999994</v>
+        <v>62.6</v>
       </c>
       <c r="C35" s="7">
-        <v>63.7</v>
+        <v>64.5</v>
       </c>
       <c r="D35" s="7">
-        <v>65.2</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="E35" s="7">
-        <v>61.5</v>
-      </c>
-      <c r="F35" s="8">
-        <v>-1.9</v>
-      </c>
-      <c r="G35" s="8">
-        <v>-2.9</v>
+        <v>62.3</v>
+      </c>
+      <c r="F35" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="G35" s="10">
+        <v>1.26</v>
       </c>
       <c r="H35" s="9">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="I35" s="9">
-        <v>0</v>
-      </c>
-      <c r="J35" s="8">
-        <v>-74.599999999999994</v>
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="I35" s="10">
+        <v>294.10000000000002</v>
+      </c>
+      <c r="J35" s="10">
+        <v>1.51</v>
       </c>
       <c r="K35" s="9">
-        <v>2.3E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="L35" s="8">
-        <v>-65.099999999999994</v>
+        <v>-59.1</v>
       </c>
       <c r="M35" s="9">
-        <v>2.0000000000000001E-4</v>
-      </c>
-      <c r="N35" s="9">
-        <v>0</v>
-      </c>
-      <c r="O35" s="8">
-        <v>-74.599999999999994</v>
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="N35" s="10">
+        <v>294.10000000000002</v>
+      </c>
+      <c r="O35" s="10">
+        <v>1.51</v>
       </c>
       <c r="P35" s="9">
-        <v>2.3E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
       <c r="Q35" s="8">
-        <v>-65.099999999999994</v>
+        <v>-59.1</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7">
-        <v>67.599999999999994</v>
+        <v>65.099999999999994</v>
       </c>
       <c r="C36" s="7">
-        <v>65.599999999999994</v>
+        <v>63.7</v>
       </c>
       <c r="D36" s="7">
-        <v>68</v>
+        <v>65.2</v>
       </c>
       <c r="E36" s="7">
-        <v>65</v>
+        <v>61.5</v>
       </c>
       <c r="F36" s="8">
-        <v>-1.7</v>
+        <v>-1.9</v>
       </c>
       <c r="G36" s="8">
-        <v>-2.5299999999999998</v>
+        <v>-2.9</v>
       </c>
       <c r="H36" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3058,10 +3058,10 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="K36" s="9">
-        <v>2.2000000000000001E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="L36" s="8">
-        <v>-63.8</v>
+        <v>-65.099999999999994</v>
       </c>
       <c r="M36" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3073,33 +3073,33 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="P36" s="9">
-        <v>2.2000000000000001E-3</v>
+        <v>2.3E-3</v>
       </c>
       <c r="Q36" s="8">
-        <v>-63.8</v>
+        <v>-65.099999999999994</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7">
-        <v>65.8</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="C37" s="7">
-        <v>67.3</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="D37" s="7">
-        <v>68.900000000000006</v>
+        <v>68</v>
       </c>
       <c r="E37" s="7">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="F37" s="10">
-        <v>1.5</v>
-      </c>
-      <c r="G37" s="10">
-        <v>2.2799999999999998</v>
+        <v>65</v>
+      </c>
+      <c r="F37" s="8">
+        <v>-1.7</v>
+      </c>
+      <c r="G37" s="8">
+        <v>-2.5299999999999998</v>
       </c>
       <c r="H37" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3111,10 +3111,10 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="K37" s="9">
-        <v>2E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="L37" s="8">
-        <v>-62.5</v>
+        <v>-63.8</v>
       </c>
       <c r="M37" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3126,33 +3126,33 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="P37" s="9">
-        <v>2E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="Q37" s="8">
-        <v>-62.5</v>
+        <v>-63.8</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7">
-        <v>67</v>
+        <v>65.8</v>
       </c>
       <c r="C38" s="7">
-        <v>65.8</v>
+        <v>67.3</v>
       </c>
       <c r="D38" s="7">
-        <v>68.8</v>
+        <v>68.900000000000006</v>
       </c>
       <c r="E38" s="7">
-        <v>62.8</v>
-      </c>
-      <c r="F38" s="8">
-        <v>-1.5</v>
-      </c>
-      <c r="G38" s="8">
-        <v>-2.23</v>
+        <v>65.599999999999994</v>
+      </c>
+      <c r="F38" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="G38" s="10">
+        <v>2.2799999999999998</v>
       </c>
       <c r="H38" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3164,10 +3164,10 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="K38" s="9">
-        <v>1.8E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="L38" s="8">
-        <v>-60.8</v>
+        <v>-62.5</v>
       </c>
       <c r="M38" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3179,33 +3179,33 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="P38" s="9">
-        <v>1.8E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="Q38" s="8">
-        <v>-60.8</v>
+        <v>-62.5</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7">
-        <v>68.5</v>
+        <v>67</v>
       </c>
       <c r="C39" s="7">
-        <v>67.3</v>
+        <v>65.8</v>
       </c>
       <c r="D39" s="7">
-        <v>70.3</v>
+        <v>68.8</v>
       </c>
       <c r="E39" s="7">
-        <v>67.099999999999994</v>
+        <v>62.8</v>
       </c>
       <c r="F39" s="8">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
       <c r="G39" s="8">
-        <v>-1.75</v>
+        <v>-2.23</v>
       </c>
       <c r="H39" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3217,10 +3217,10 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="K39" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="L39" s="8">
-        <v>-58.2</v>
+        <v>-60.8</v>
       </c>
       <c r="M39" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3232,33 +3232,33 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="P39" s="9">
-        <v>1.6999999999999999E-3</v>
+        <v>1.8E-3</v>
       </c>
       <c r="Q39" s="8">
-        <v>-58.2</v>
+        <v>-60.8</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7">
-        <v>70.099999999999994</v>
+        <v>68.5</v>
       </c>
       <c r="C40" s="7">
-        <v>68.5</v>
+        <v>67.3</v>
       </c>
       <c r="D40" s="7">
-        <v>71.900000000000006</v>
+        <v>70.3</v>
       </c>
       <c r="E40" s="7">
-        <v>67.400000000000006</v>
+        <v>67.099999999999994</v>
       </c>
       <c r="F40" s="8">
-        <v>-1.5</v>
+        <v>-1.2</v>
       </c>
       <c r="G40" s="8">
-        <v>-2.14</v>
+        <v>-1.75</v>
       </c>
       <c r="H40" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3270,10 +3270,10 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="K40" s="9">
-        <v>1.5E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="L40" s="8">
-        <v>-55</v>
+        <v>-58.2</v>
       </c>
       <c r="M40" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3285,33 +3285,33 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="P40" s="9">
-        <v>1.5E-3</v>
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="Q40" s="8">
-        <v>-55</v>
+        <v>-58.2</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7">
-        <v>68</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="C41" s="7">
-        <v>70</v>
+        <v>68.5</v>
       </c>
       <c r="D41" s="7">
-        <v>72</v>
+        <v>71.900000000000006</v>
       </c>
       <c r="E41" s="7">
         <v>67.400000000000006</v>
       </c>
-      <c r="F41" s="10">
-        <v>2.6</v>
-      </c>
-      <c r="G41" s="10">
-        <v>3.86</v>
+      <c r="F41" s="8">
+        <v>-1.5</v>
+      </c>
+      <c r="G41" s="8">
+        <v>-2.14</v>
       </c>
       <c r="H41" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3323,10 +3323,10 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="K41" s="9">
-        <v>1.2999999999999999E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="L41" s="8">
-        <v>-49.8</v>
+        <v>-55</v>
       </c>
       <c r="M41" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3338,33 +3338,33 @@
         <v>-74.599999999999994</v>
       </c>
       <c r="P41" s="9">
-        <v>1.2999999999999999E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="Q41" s="8">
-        <v>-49.8</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7">
+        <v>68</v>
+      </c>
+      <c r="C42" s="7">
         <v>70</v>
       </c>
-      <c r="C42" s="7">
+      <c r="D42" s="7">
+        <v>72</v>
+      </c>
+      <c r="E42" s="7">
         <v>67.400000000000006</v>
       </c>
-      <c r="D42" s="7">
-        <v>74</v>
-      </c>
-      <c r="E42" s="7">
-        <v>67.2</v>
-      </c>
-      <c r="F42" s="8">
-        <v>-2.1</v>
-      </c>
-      <c r="G42" s="8">
-        <v>-3.02</v>
+      <c r="F42" s="10">
+        <v>2.6</v>
+      </c>
+      <c r="G42" s="10">
+        <v>3.86</v>
       </c>
       <c r="H42" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3373,13 +3373,13 @@
         <v>0</v>
       </c>
       <c r="J42" s="8">
-        <v>-74.2</v>
+        <v>-74.599999999999994</v>
       </c>
       <c r="K42" s="9">
-        <v>1.1999999999999999E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="L42" s="8">
-        <v>-41.5</v>
+        <v>-49.8</v>
       </c>
       <c r="M42" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3388,36 +3388,36 @@
         <v>0</v>
       </c>
       <c r="O42" s="8">
-        <v>-74.2</v>
+        <v>-74.599999999999994</v>
       </c>
       <c r="P42" s="9">
-        <v>1.1999999999999999E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q42" s="8">
-        <v>-41.5</v>
+        <v>-49.8</v>
       </c>
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7">
-        <v>73.5</v>
+        <v>70</v>
       </c>
       <c r="C43" s="7">
-        <v>69.5</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="D43" s="7">
-        <v>75.099999999999994</v>
+        <v>74</v>
       </c>
       <c r="E43" s="7">
-        <v>69</v>
+        <v>67.2</v>
       </c>
       <c r="F43" s="8">
-        <v>-3.8</v>
+        <v>-2.1</v>
       </c>
       <c r="G43" s="8">
-        <v>-5.18</v>
+        <v>-3.02</v>
       </c>
       <c r="H43" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3426,13 +3426,13 @@
         <v>0</v>
       </c>
       <c r="J43" s="8">
-        <v>-74.599999999999994</v>
+        <v>-74.2</v>
       </c>
       <c r="K43" s="9">
-        <v>1E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="L43" s="8">
-        <v>-24.8</v>
+        <v>-41.5</v>
       </c>
       <c r="M43" s="9">
         <v>2.0000000000000001E-4</v>
@@ -3441,154 +3441,154 @@
         <v>0</v>
       </c>
       <c r="O43" s="8">
-        <v>-74.599999999999994</v>
+        <v>-74.2</v>
       </c>
       <c r="P43" s="9">
-        <v>1E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="Q43" s="8">
-        <v>-24.8</v>
+        <v>-41.5</v>
       </c>
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7">
-        <v>74.5</v>
+        <v>73.5</v>
       </c>
       <c r="C44" s="7">
-        <v>73.3</v>
+        <v>69.5</v>
       </c>
       <c r="D44" s="7">
-        <v>78.099999999999994</v>
+        <v>75.099999999999994</v>
       </c>
       <c r="E44" s="7">
-        <v>72.5</v>
+        <v>69</v>
       </c>
       <c r="F44" s="8">
-        <v>-1.9</v>
+        <v>-3.8</v>
       </c>
       <c r="G44" s="8">
-        <v>-2.5299999999999998</v>
+        <v>-5.18</v>
       </c>
       <c r="H44" s="9">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="I44" s="8">
-        <v>-74.599999999999994</v>
+      <c r="I44" s="9">
+        <v>0</v>
       </c>
       <c r="J44" s="8">
         <v>-74.599999999999994</v>
       </c>
       <c r="K44" s="9">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="L44" s="10">
-        <v>25.4</v>
+        <v>1E-3</v>
+      </c>
+      <c r="L44" s="8">
+        <v>-24.8</v>
       </c>
       <c r="M44" s="9">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="N44" s="8">
-        <v>-74.599999999999994</v>
+      <c r="N44" s="9">
+        <v>0</v>
       </c>
       <c r="O44" s="8">
         <v>-74.599999999999994</v>
       </c>
       <c r="P44" s="9">
-        <v>8.0000000000000004E-4</v>
-      </c>
-      <c r="Q44" s="10">
-        <v>25.4</v>
+        <v>1E-3</v>
+      </c>
+      <c r="Q44" s="8">
+        <v>-24.8</v>
       </c>
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7">
-        <v>71.099999999999994</v>
+        <v>74.5</v>
       </c>
       <c r="C45" s="7">
-        <v>75.2</v>
+        <v>73.3</v>
       </c>
       <c r="D45" s="7">
-        <v>79.5</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="E45" s="7">
-        <v>70.7</v>
-      </c>
-      <c r="F45" s="10">
-        <v>3.2</v>
-      </c>
-      <c r="G45" s="10">
-        <v>4.4400000000000004</v>
+        <v>72.5</v>
+      </c>
+      <c r="F45" s="8">
+        <v>-1.9</v>
+      </c>
+      <c r="G45" s="8">
+        <v>-2.5299999999999998</v>
       </c>
       <c r="H45" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="I45" s="10">
-        <v>1.51</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>17</v>
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="I45" s="8">
+        <v>-74.599999999999994</v>
+      </c>
+      <c r="J45" s="8">
+        <v>-74.599999999999994</v>
       </c>
       <c r="K45" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>17</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="L45" s="10">
+        <v>25.4</v>
       </c>
       <c r="M45" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="N45" s="10">
-        <v>1.51</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>17</v>
+        <v>2.0000000000000001E-4</v>
+      </c>
+      <c r="N45" s="8">
+        <v>-74.599999999999994</v>
+      </c>
+      <c r="O45" s="8">
+        <v>-74.599999999999994</v>
       </c>
       <c r="P45" s="9">
-        <v>6.9999999999999999E-4</v>
-      </c>
-      <c r="Q45" s="9" t="s">
-        <v>17</v>
+        <v>8.0000000000000004E-4</v>
+      </c>
+      <c r="Q45" s="10">
+        <v>25.4</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7">
-        <v>73.900000000000006</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="C46" s="7">
-        <v>72</v>
+        <v>75.2</v>
       </c>
       <c r="D46" s="7">
-        <v>81.5</v>
+        <v>79.5</v>
       </c>
       <c r="E46" s="7">
-        <v>69</v>
-      </c>
-      <c r="F46" s="8">
-        <v>-0.4</v>
-      </c>
-      <c r="G46" s="8">
-        <v>-0.55000000000000004</v>
+        <v>70.7</v>
+      </c>
+      <c r="F46" s="10">
+        <v>3.2</v>
+      </c>
+      <c r="G46" s="10">
+        <v>4.4400000000000004</v>
       </c>
       <c r="H46" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I46" s="8">
-        <v>-1.49</v>
+      <c r="I46" s="10">
+        <v>1.51</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K46" s="9">
-        <v>7.3000000000000001E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="L46" s="9" t="s">
         <v>17</v>
@@ -3596,14 +3596,14 @@
       <c r="M46" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="N46" s="8">
-        <v>-1.49</v>
+      <c r="N46" s="10">
+        <v>1.51</v>
       </c>
       <c r="O46" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P46" s="9">
-        <v>7.3000000000000001E-3</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q46" s="9" t="s">
         <v>17</v>
@@ -3611,37 +3611,37 @@
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="C47" s="7">
+        <v>72</v>
+      </c>
+      <c r="D47" s="7">
+        <v>81.5</v>
+      </c>
+      <c r="E47" s="7">
         <v>69</v>
       </c>
-      <c r="C47" s="7">
-        <v>72.400000000000006</v>
-      </c>
-      <c r="D47" s="7">
-        <v>75.2</v>
-      </c>
-      <c r="E47" s="7">
-        <v>66.099999999999994</v>
-      </c>
-      <c r="F47" s="10">
-        <v>3.9</v>
-      </c>
-      <c r="G47" s="10">
-        <v>5.69</v>
+      <c r="F47" s="8">
+        <v>-0.4</v>
+      </c>
+      <c r="G47" s="8">
+        <v>-0.55000000000000004</v>
       </c>
       <c r="H47" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I47" s="9">
-        <v>0</v>
+      <c r="I47" s="8">
+        <v>-1.49</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K47" s="9">
-        <v>6.7000000000000002E-3</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="L47" s="9" t="s">
         <v>17</v>
@@ -3649,14 +3649,14 @@
       <c r="M47" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="N47" s="9">
-        <v>0</v>
+      <c r="N47" s="8">
+        <v>-1.49</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P47" s="9">
-        <v>6.7000000000000002E-3</v>
+        <v>7.3000000000000001E-3</v>
       </c>
       <c r="Q47" s="9" t="s">
         <v>17</v>
@@ -3664,25 +3664,25 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7">
-        <v>69.8</v>
+        <v>69</v>
       </c>
       <c r="C48" s="7">
-        <v>68.5</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="D48" s="7">
-        <v>87</v>
+        <v>75.2</v>
       </c>
       <c r="E48" s="7">
-        <v>64</v>
-      </c>
-      <c r="F48" s="8">
-        <v>-1.7</v>
-      </c>
-      <c r="G48" s="8">
-        <v>-2.42</v>
+        <v>66.099999999999994</v>
+      </c>
+      <c r="F48" s="10">
+        <v>3.9</v>
+      </c>
+      <c r="G48" s="10">
+        <v>5.69</v>
       </c>
       <c r="H48" s="9">
         <v>6.9999999999999999E-4</v>
@@ -3694,7 +3694,7 @@
         <v>17</v>
       </c>
       <c r="K48" s="9">
-        <v>6.0000000000000001E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="L48" s="9" t="s">
         <v>17</v>
@@ -3709,7 +3709,7 @@
         <v>17</v>
       </c>
       <c r="P48" s="9">
-        <v>6.0000000000000001E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="Q48" s="9" t="s">
         <v>17</v>
@@ -3717,25 +3717,25 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7">
-        <v>69</v>
+        <v>69.8</v>
       </c>
       <c r="C49" s="7">
-        <v>70.2</v>
+        <v>68.5</v>
       </c>
       <c r="D49" s="7">
-        <v>76.400000000000006</v>
+        <v>87</v>
       </c>
       <c r="E49" s="7">
-        <v>68</v>
-      </c>
-      <c r="F49" s="10">
-        <v>1.7</v>
-      </c>
-      <c r="G49" s="10">
-        <v>2.48</v>
+        <v>64</v>
+      </c>
+      <c r="F49" s="8">
+        <v>-1.7</v>
+      </c>
+      <c r="G49" s="8">
+        <v>-2.42</v>
       </c>
       <c r="H49" s="9">
         <v>6.9999999999999999E-4</v>
@@ -3747,7 +3747,7 @@
         <v>17</v>
       </c>
       <c r="K49" s="9">
-        <v>5.3E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="L49" s="9" t="s">
         <v>17</v>
@@ -3762,7 +3762,7 @@
         <v>17</v>
       </c>
       <c r="P49" s="9">
-        <v>5.3E-3</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q49" s="9" t="s">
         <v>17</v>
@@ -3770,25 +3770,25 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C50" s="7">
-        <v>68.5</v>
+        <v>70.2</v>
       </c>
       <c r="D50" s="7">
-        <v>76</v>
+        <v>76.400000000000006</v>
       </c>
       <c r="E50" s="7">
-        <v>65.8</v>
-      </c>
-      <c r="F50" s="8">
-        <v>-7.1</v>
-      </c>
-      <c r="G50" s="8">
-        <v>-9.39</v>
+        <v>68</v>
+      </c>
+      <c r="F50" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="G50" s="10">
+        <v>2.48</v>
       </c>
       <c r="H50" s="9">
         <v>6.9999999999999999E-4</v>
@@ -3800,7 +3800,7 @@
         <v>17</v>
       </c>
       <c r="K50" s="9">
-        <v>4.7000000000000002E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="L50" s="9" t="s">
         <v>17</v>
@@ -3815,7 +3815,7 @@
         <v>17</v>
       </c>
       <c r="P50" s="9">
-        <v>4.7000000000000002E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="Q50" s="9" t="s">
         <v>17</v>
@@ -3823,25 +3823,25 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
+        <v>43313</v>
       </c>
       <c r="B51" s="7">
-        <v>81.900000000000006</v>
+        <v>75</v>
       </c>
       <c r="C51" s="7">
-        <v>75.599999999999994</v>
+        <v>68.5</v>
       </c>
       <c r="D51" s="7">
-        <v>82.9</v>
+        <v>76</v>
       </c>
       <c r="E51" s="7">
-        <v>72</v>
+        <v>65.8</v>
       </c>
       <c r="F51" s="8">
-        <v>-5.0999999999999996</v>
+        <v>-7.1</v>
       </c>
       <c r="G51" s="8">
-        <v>-6.32</v>
+        <v>-9.39</v>
       </c>
       <c r="H51" s="9">
         <v>6.9999999999999999E-4</v>
@@ -3853,7 +3853,7 @@
         <v>17</v>
       </c>
       <c r="K51" s="9">
-        <v>4.0000000000000001E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="L51" s="9" t="s">
         <v>17</v>
@@ -3868,7 +3868,7 @@
         <v>17</v>
       </c>
       <c r="P51" s="9">
-        <v>4.0000000000000001E-3</v>
+        <v>4.7000000000000002E-3</v>
       </c>
       <c r="Q51" s="9" t="s">
         <v>17</v>
@@ -3876,25 +3876,25 @@
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7">
-        <v>89.1</v>
+        <v>81.900000000000006</v>
       </c>
       <c r="C52" s="7">
-        <v>80.7</v>
+        <v>75.599999999999994</v>
       </c>
       <c r="D52" s="7">
-        <v>95.9</v>
+        <v>82.9</v>
       </c>
       <c r="E52" s="7">
-        <v>80.099999999999994</v>
+        <v>72</v>
       </c>
       <c r="F52" s="8">
-        <v>-9.1</v>
+        <v>-5.0999999999999996</v>
       </c>
       <c r="G52" s="8">
-        <v>-10.130000000000001</v>
+        <v>-6.32</v>
       </c>
       <c r="H52" s="9">
         <v>6.9999999999999999E-4</v>
@@ -3906,7 +3906,7 @@
         <v>17</v>
       </c>
       <c r="K52" s="9">
-        <v>3.3E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="L52" s="9" t="s">
         <v>17</v>
@@ -3921,7 +3921,7 @@
         <v>17</v>
       </c>
       <c r="P52" s="9">
-        <v>3.3E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="Q52" s="9" t="s">
         <v>17</v>
@@ -3929,37 +3929,37 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7">
-        <v>106</v>
+        <v>89.1</v>
       </c>
       <c r="C53" s="7">
-        <v>89.8</v>
+        <v>80.7</v>
       </c>
       <c r="D53" s="7">
-        <v>111</v>
+        <v>95.9</v>
       </c>
       <c r="E53" s="7">
-        <v>81</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="F53" s="8">
-        <v>-16.2</v>
+        <v>-9.1</v>
       </c>
       <c r="G53" s="8">
-        <v>-15.28</v>
+        <v>-10.130000000000001</v>
       </c>
       <c r="H53" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I53" s="10">
-        <v>1.51</v>
+      <c r="I53" s="9">
+        <v>0</v>
       </c>
       <c r="J53" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K53" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="L53" s="9" t="s">
         <v>17</v>
@@ -3967,14 +3967,14 @@
       <c r="M53" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="N53" s="10">
-        <v>1.51</v>
+      <c r="N53" s="9">
+        <v>0</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P53" s="9">
-        <v>2.7000000000000001E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="Q53" s="9" t="s">
         <v>17</v>
@@ -3982,37 +3982,37 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7">
-        <v>89.4</v>
+        <v>106</v>
       </c>
       <c r="C54" s="7">
-        <v>106</v>
+        <v>89.8</v>
       </c>
       <c r="D54" s="7">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E54" s="7">
-        <v>88</v>
-      </c>
-      <c r="F54" s="10">
-        <v>18.8</v>
-      </c>
-      <c r="G54" s="10">
-        <v>21.56</v>
+        <v>81</v>
+      </c>
+      <c r="F54" s="8">
+        <v>-16.2</v>
+      </c>
+      <c r="G54" s="8">
+        <v>-15.28</v>
       </c>
       <c r="H54" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I54" s="8">
-        <v>-1.49</v>
+      <c r="I54" s="10">
+        <v>1.51</v>
       </c>
       <c r="J54" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K54" s="9">
-        <v>2E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="L54" s="9" t="s">
         <v>17</v>
@@ -4020,14 +4020,14 @@
       <c r="M54" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="N54" s="8">
-        <v>-1.49</v>
+      <c r="N54" s="10">
+        <v>1.51</v>
       </c>
       <c r="O54" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P54" s="9">
-        <v>2E-3</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="Q54" s="9" t="s">
         <v>17</v>
@@ -4035,37 +4035,37 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7">
-        <v>65</v>
+        <v>89.4</v>
       </c>
       <c r="C55" s="7">
-        <v>87.2</v>
+        <v>106</v>
       </c>
       <c r="D55" s="7">
-        <v>99.5</v>
+        <v>129</v>
       </c>
       <c r="E55" s="7">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="F55" s="10">
-        <v>22.6</v>
+        <v>18.8</v>
       </c>
       <c r="G55" s="10">
-        <v>34.979999999999997</v>
+        <v>21.56</v>
       </c>
       <c r="H55" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I55" s="9">
-        <v>0</v>
+      <c r="I55" s="8">
+        <v>-1.49</v>
       </c>
       <c r="J55" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K55" s="9">
-        <v>1.2999999999999999E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="L55" s="9" t="s">
         <v>17</v>
@@ -4073,14 +4073,14 @@
       <c r="M55" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="N55" s="9">
-        <v>0</v>
+      <c r="N55" s="8">
+        <v>-1.49</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P55" s="9">
-        <v>1.2999999999999999E-3</v>
+        <v>2E-3</v>
       </c>
       <c r="Q55" s="9" t="s">
         <v>17</v>
@@ -4088,37 +4088,37 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7">
-        <v>69.3</v>
+        <v>65</v>
       </c>
       <c r="C56" s="7">
-        <v>64.599999999999994</v>
+        <v>87.2</v>
       </c>
       <c r="D56" s="7">
-        <v>70</v>
+        <v>99.5</v>
       </c>
       <c r="E56" s="7">
-        <v>63.6</v>
-      </c>
-      <c r="F56" s="8">
-        <v>-5.5</v>
-      </c>
-      <c r="G56" s="8">
-        <v>-7.85</v>
+        <v>64</v>
+      </c>
+      <c r="F56" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="G56" s="10">
+        <v>34.979999999999997</v>
       </c>
       <c r="H56" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="I56" s="9" t="s">
-        <v>17</v>
+      <c r="I56" s="9">
+        <v>0</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>17</v>
       </c>
       <c r="K56" s="9">
-        <v>6.9999999999999999E-4</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="L56" s="9" t="s">
         <v>17</v>
@@ -4126,14 +4126,14 @@
       <c r="M56" s="9">
         <v>6.9999999999999999E-4</v>
       </c>
-      <c r="N56" s="9" t="s">
-        <v>17</v>
+      <c r="N56" s="9">
+        <v>0</v>
       </c>
       <c r="O56" s="9" t="s">
         <v>17</v>
       </c>
       <c r="P56" s="9">
-        <v>6.9999999999999999E-4</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q56" s="9" t="s">
         <v>17</v>
@@ -4141,28 +4141,28 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7">
-        <v>66.2</v>
+        <v>69.3</v>
       </c>
       <c r="C57" s="7">
-        <v>70.099999999999994</v>
+        <v>64.599999999999994</v>
       </c>
       <c r="D57" s="7">
-        <v>76.3</v>
+        <v>70</v>
       </c>
       <c r="E57" s="7">
-        <v>63</v>
-      </c>
-      <c r="F57" s="10">
-        <v>2.4</v>
-      </c>
-      <c r="G57" s="10">
-        <v>3.55</v>
+        <v>63.6</v>
+      </c>
+      <c r="F57" s="8">
+        <v>-5.5</v>
+      </c>
+      <c r="G57" s="8">
+        <v>-7.85</v>
       </c>
       <c r="H57" s="9">
-        <v>0</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="I57" s="9" t="s">
         <v>17</v>
@@ -4171,13 +4171,13 @@
         <v>17</v>
       </c>
       <c r="K57" s="9">
-        <v>0</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="L57" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M57" s="9">
-        <v>0</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>17</v>
@@ -4186,7 +4186,7 @@
         <v>17</v>
       </c>
       <c r="P57" s="9">
-        <v>0</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="Q57" s="9" t="s">
         <v>17</v>
@@ -4194,25 +4194,25 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B58" s="7">
-        <v>71.099999999999994</v>
+        <v>66.2</v>
       </c>
       <c r="C58" s="7">
-        <v>67.7</v>
+        <v>70.099999999999994</v>
       </c>
       <c r="D58" s="7">
-        <v>72.599999999999994</v>
+        <v>76.3</v>
       </c>
       <c r="E58" s="7">
-        <v>65</v>
-      </c>
-      <c r="F58" s="8">
-        <v>-3.2</v>
-      </c>
-      <c r="G58" s="8">
-        <v>-4.51</v>
+        <v>63</v>
+      </c>
+      <c r="F58" s="10">
+        <v>2.4</v>
+      </c>
+      <c r="G58" s="10">
+        <v>3.55</v>
       </c>
       <c r="H58" s="9">
         <v>0</v>
@@ -4226,8 +4226,8 @@
       <c r="K58" s="9">
         <v>0</v>
       </c>
-      <c r="L58" s="8">
-        <v>-100</v>
+      <c r="L58" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M58" s="9">
         <v>0</v>
@@ -4241,31 +4241,31 @@
       <c r="P58" s="9">
         <v>0</v>
       </c>
-      <c r="Q58" s="8">
-        <v>-100</v>
+      <c r="Q58" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B59" s="7">
-        <v>77</v>
+        <v>71.099999999999994</v>
       </c>
       <c r="C59" s="7">
-        <v>70.900000000000006</v>
+        <v>67.7</v>
       </c>
       <c r="D59" s="7">
-        <v>77.099999999999994</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="E59" s="7">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F59" s="8">
-        <v>-6.1</v>
+        <v>-3.2</v>
       </c>
       <c r="G59" s="8">
-        <v>-7.92</v>
+        <v>-4.51</v>
       </c>
       <c r="H59" s="9">
         <v>0</v>
@@ -4300,25 +4300,25 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B60" s="7">
-        <v>79.400000000000006</v>
+        <v>77</v>
       </c>
       <c r="C60" s="7">
-        <v>77</v>
+        <v>70.900000000000006</v>
       </c>
       <c r="D60" s="7">
-        <v>84.9</v>
+        <v>77.099999999999994</v>
       </c>
       <c r="E60" s="7">
-        <v>76.3</v>
+        <v>69</v>
       </c>
       <c r="F60" s="8">
-        <v>-1.1000000000000001</v>
+        <v>-6.1</v>
       </c>
       <c r="G60" s="8">
-        <v>-1.41</v>
+        <v>-7.92</v>
       </c>
       <c r="H60" s="9">
         <v>0</v>
@@ -4353,25 +4353,25 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B61" s="7">
-        <v>70.400000000000006</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="C61" s="7">
-        <v>78.099999999999994</v>
+        <v>77</v>
       </c>
       <c r="D61" s="7">
-        <v>95.5</v>
+        <v>84.9</v>
       </c>
       <c r="E61" s="7">
-        <v>64.5</v>
-      </c>
-      <c r="F61" s="10">
-        <v>9.9</v>
-      </c>
-      <c r="G61" s="10">
-        <v>14.52</v>
+        <v>76.3</v>
+      </c>
+      <c r="F61" s="8">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="G61" s="8">
+        <v>-1.41</v>
       </c>
       <c r="H61" s="9">
         <v>0</v>
@@ -4379,8 +4379,8 @@
       <c r="I61" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J61" s="8">
-        <v>-100</v>
+      <c r="J61" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K61" s="9">
         <v>0</v>
@@ -4394,8 +4394,8 @@
       <c r="N61" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O61" s="8">
-        <v>-100</v>
+      <c r="O61" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P61" s="9">
         <v>0</v>
@@ -4406,25 +4406,25 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B62" s="7">
-        <v>93.5</v>
+        <v>70.400000000000006</v>
       </c>
       <c r="C62" s="7">
-        <v>68.2</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="D62" s="7">
-        <v>93.8</v>
+        <v>95.5</v>
       </c>
       <c r="E62" s="7">
-        <v>64.3</v>
-      </c>
-      <c r="F62" s="8">
-        <v>-25</v>
-      </c>
-      <c r="G62" s="8">
-        <v>-26.82</v>
+        <v>64.5</v>
+      </c>
+      <c r="F62" s="10">
+        <v>9.9</v>
+      </c>
+      <c r="G62" s="10">
+        <v>14.52</v>
       </c>
       <c r="H62" s="9">
         <v>0</v>
@@ -4432,14 +4432,14 @@
       <c r="I62" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J62" s="9" t="s">
-        <v>17</v>
+      <c r="J62" s="8">
+        <v>-100</v>
       </c>
       <c r="K62" s="9">
         <v>0</v>
       </c>
-      <c r="L62" s="9" t="s">
-        <v>17</v>
+      <c r="L62" s="8">
+        <v>-100</v>
       </c>
       <c r="M62" s="9">
         <v>0</v>
@@ -4447,37 +4447,37 @@
       <c r="N62" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O62" s="9" t="s">
-        <v>17</v>
+      <c r="O62" s="8">
+        <v>-100</v>
       </c>
       <c r="P62" s="9">
         <v>0</v>
       </c>
-      <c r="Q62" s="9" t="s">
-        <v>17</v>
+      <c r="Q62" s="8">
+        <v>-100</v>
       </c>
     </row>
     <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
-        <v>42917</v>
+        <v>42948</v>
       </c>
       <c r="B63" s="7">
-        <v>124</v>
+        <v>93.5</v>
       </c>
       <c r="C63" s="7">
-        <v>93.2</v>
+        <v>68.2</v>
       </c>
       <c r="D63" s="7">
-        <v>124</v>
+        <v>93.8</v>
       </c>
       <c r="E63" s="7">
-        <v>88.3</v>
+        <v>64.3</v>
       </c>
       <c r="F63" s="8">
-        <v>-29.8</v>
+        <v>-25</v>
       </c>
       <c r="G63" s="8">
-        <v>-24.23</v>
+        <v>-26.82</v>
       </c>
       <c r="H63" s="9">
         <v>0</v>
@@ -4512,25 +4512,25 @@
     </row>
     <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
-        <v>42887</v>
+        <v>42917</v>
       </c>
       <c r="B64" s="7">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C64" s="7">
-        <v>123</v>
+        <v>93.2</v>
       </c>
       <c r="D64" s="7">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E64" s="7">
-        <v>120</v>
+        <v>88.3</v>
       </c>
       <c r="F64" s="8">
-        <v>-2.5</v>
+        <v>-29.8</v>
       </c>
       <c r="G64" s="8">
-        <v>-1.99</v>
+        <v>-24.23</v>
       </c>
       <c r="H64" s="9">
         <v>0</v>
@@ -4565,25 +4565,25 @@
     </row>
     <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
-        <v>42856</v>
+        <v>42887</v>
       </c>
       <c r="B65" s="7">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="C65" s="7">
-        <v>125.5</v>
+        <v>123</v>
       </c>
       <c r="D65" s="7">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="E65" s="7">
-        <v>116.5</v>
+        <v>120</v>
       </c>
       <c r="F65" s="8">
-        <v>-22.5</v>
+        <v>-2.5</v>
       </c>
       <c r="G65" s="8">
-        <v>-15.2</v>
+        <v>-1.99</v>
       </c>
       <c r="H65" s="9">
         <v>0</v>
@@ -4618,25 +4618,25 @@
     </row>
     <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
-        <v>42826</v>
+        <v>42856</v>
       </c>
       <c r="B66" s="7">
-        <v>160.5</v>
+        <v>148</v>
       </c>
       <c r="C66" s="7">
+        <v>125.5</v>
+      </c>
+      <c r="D66" s="7">
         <v>148</v>
       </c>
-      <c r="D66" s="7">
-        <v>165</v>
-      </c>
       <c r="E66" s="7">
-        <v>137.5</v>
+        <v>116.5</v>
       </c>
       <c r="F66" s="8">
-        <v>-14</v>
+        <v>-22.5</v>
       </c>
       <c r="G66" s="8">
-        <v>-8.64</v>
+        <v>-15.2</v>
       </c>
       <c r="H66" s="9">
         <v>0</v>
@@ -4671,25 +4671,25 @@
     </row>
     <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
-        <v>42795</v>
-      </c>
-      <c r="B67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F67" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>17</v>
+        <v>42826</v>
+      </c>
+      <c r="B67" s="7">
+        <v>160.5</v>
+      </c>
+      <c r="C67" s="7">
+        <v>148</v>
+      </c>
+      <c r="D67" s="7">
+        <v>165</v>
+      </c>
+      <c r="E67" s="7">
+        <v>137.5</v>
+      </c>
+      <c r="F67" s="8">
+        <v>-14</v>
+      </c>
+      <c r="G67" s="8">
+        <v>-8.64</v>
       </c>
       <c r="H67" s="9">
         <v>0</v>
@@ -4724,7 +4724,7 @@
     </row>
     <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
-        <v>42767</v>
+        <v>42795</v>
       </c>
       <c r="B68" s="7" t="s">
         <v>17</v>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
-        <v>42736</v>
+        <v>42767</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>17</v>
@@ -4830,7 +4830,7 @@
     </row>
     <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
-        <v>42705</v>
+        <v>42736</v>
       </c>
       <c r="B70" s="7" t="s">
         <v>17</v>
@@ -4860,7 +4860,7 @@
         <v>17</v>
       </c>
       <c r="K70" s="9">
-        <v>1.2999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="L70" s="9" t="s">
         <v>17</v>
@@ -4875,7 +4875,7 @@
         <v>17</v>
       </c>
       <c r="P70" s="9">
-        <v>1.2999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="Q70" s="9" t="s">
         <v>17</v>
@@ -4883,7 +4883,7 @@
     </row>
     <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
-        <v>42675</v>
+        <v>42705</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>17</v>
@@ -4936,7 +4936,7 @@
     </row>
     <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
-        <v>42644</v>
+        <v>42675</v>
       </c>
       <c r="B72" s="7" t="s">
         <v>17</v>
@@ -4959,8 +4959,8 @@
       <c r="H72" s="9">
         <v>0</v>
       </c>
-      <c r="I72" s="8">
-        <v>-100</v>
+      <c r="I72" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J72" s="9" t="s">
         <v>17</v>
@@ -4974,8 +4974,8 @@
       <c r="M72" s="9">
         <v>0</v>
       </c>
-      <c r="N72" s="8">
-        <v>-100</v>
+      <c r="N72" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O72" s="9" t="s">
         <v>17</v>
@@ -4989,7 +4989,7 @@
     </row>
     <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
-        <v>42614</v>
+        <v>42644</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>17</v>
@@ -5010,10 +5010,10 @@
         <v>17</v>
       </c>
       <c r="H73" s="9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="I73" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I73" s="8">
+        <v>-100</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>17</v>
@@ -5025,10 +5025,10 @@
         <v>17</v>
       </c>
       <c r="M73" s="9">
-        <v>1.2999999999999999E-3</v>
-      </c>
-      <c r="N73" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N73" s="8">
+        <v>-100</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>17</v>
@@ -5042,7 +5042,7 @@
     </row>
     <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
-        <v>42583</v>
+        <v>42614</v>
       </c>
       <c r="B74" s="7" t="s">
         <v>17</v>
@@ -5063,7 +5063,7 @@
         <v>17</v>
       </c>
       <c r="H74" s="9">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="I74" s="9" t="s">
         <v>17</v>
@@ -5072,13 +5072,13 @@
         <v>17</v>
       </c>
       <c r="K74" s="9">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="L74" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M74" s="9">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="N74" s="9" t="s">
         <v>17</v>
@@ -5087,7 +5087,7 @@
         <v>17</v>
       </c>
       <c r="P74" s="9">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q74" s="9" t="s">
         <v>17</v>
@@ -5095,7 +5095,7 @@
     </row>
     <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
-        <v>42552</v>
+        <v>42583</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>17</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
-        <v>42522</v>
+        <v>42552</v>
       </c>
       <c r="B76" s="7" t="s">
         <v>17</v>
@@ -5201,7 +5201,7 @@
     </row>
     <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
-        <v>42491</v>
+        <v>42522</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>17</v>
@@ -5254,7 +5254,7 @@
     </row>
     <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
-        <v>42461</v>
+        <v>42491</v>
       </c>
       <c r="B78" s="7" t="s">
         <v>17</v>
@@ -5307,7 +5307,7 @@
     </row>
     <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
-        <v>42430</v>
+        <v>42461</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>17</v>
@@ -5360,7 +5360,7 @@
     </row>
     <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
-        <v>42401</v>
+        <v>42430</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>17</v>
@@ -5413,7 +5413,7 @@
     </row>
     <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
-        <v>42370</v>
+        <v>42401</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>17</v>
@@ -5466,7 +5466,7 @@
     </row>
     <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
-        <v>42339</v>
+        <v>42370</v>
       </c>
       <c r="B82" s="7" t="s">
         <v>17</v>
@@ -5498,8 +5498,8 @@
       <c r="K82" s="9">
         <v>0</v>
       </c>
-      <c r="L82" s="8">
-        <v>-100</v>
+      <c r="L82" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M82" s="9">
         <v>0</v>
@@ -5513,13 +5513,13 @@
       <c r="P82" s="9">
         <v>0</v>
       </c>
-      <c r="Q82" s="8">
-        <v>-100</v>
+      <c r="Q82" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
-        <v>42309</v>
+        <v>42339</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>17</v>
@@ -5572,7 +5572,7 @@
     </row>
     <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
-        <v>42278</v>
+        <v>42309</v>
       </c>
       <c r="B84" s="7" t="s">
         <v>17</v>
@@ -5598,8 +5598,8 @@
       <c r="I84" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J84" s="8">
-        <v>-100</v>
+      <c r="J84" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K84" s="9">
         <v>0</v>
@@ -5613,8 +5613,8 @@
       <c r="N84" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O84" s="8">
-        <v>-100</v>
+      <c r="O84" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P84" s="9">
         <v>0</v>
@@ -5625,7 +5625,7 @@
     </row>
     <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
-        <v>42248</v>
+        <v>42278</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>17</v>
@@ -5678,7 +5678,7 @@
     </row>
     <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
-        <v>42217</v>
+        <v>42248</v>
       </c>
       <c r="B86" s="7" t="s">
         <v>17</v>
@@ -5731,7 +5731,7 @@
     </row>
     <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
-        <v>42186</v>
+        <v>42217</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>17</v>
@@ -5784,7 +5784,7 @@
     </row>
     <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
-        <v>42156</v>
+        <v>42186</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>17</v>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
-        <v>42125</v>
+        <v>42156</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>17</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
-        <v>42095</v>
+        <v>42125</v>
       </c>
       <c r="B90" s="7" t="s">
         <v>17</v>
@@ -5943,7 +5943,7 @@
     </row>
     <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
-        <v>42064</v>
+        <v>42095</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>17</v>
@@ -5969,14 +5969,14 @@
       <c r="I91" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J91" s="9" t="s">
-        <v>17</v>
+      <c r="J91" s="8">
+        <v>-100</v>
       </c>
       <c r="K91" s="9">
         <v>0</v>
       </c>
-      <c r="L91" s="9" t="s">
-        <v>17</v>
+      <c r="L91" s="8">
+        <v>-100</v>
       </c>
       <c r="M91" s="9">
         <v>0</v>
@@ -5984,19 +5984,19 @@
       <c r="N91" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O91" s="9" t="s">
-        <v>17</v>
+      <c r="O91" s="8">
+        <v>-100</v>
       </c>
       <c r="P91" s="9">
         <v>0</v>
       </c>
-      <c r="Q91" s="9" t="s">
-        <v>17</v>
+      <c r="Q91" s="8">
+        <v>-100</v>
       </c>
     </row>
     <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
-        <v>42036</v>
+        <v>42064</v>
       </c>
       <c r="B92" s="7" t="s">
         <v>17</v>
@@ -6049,7 +6049,7 @@
     </row>
     <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
-        <v>42005</v>
+        <v>42036</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>17</v>
@@ -6102,7 +6102,7 @@
     </row>
     <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
-        <v>41974</v>
+        <v>42005</v>
       </c>
       <c r="B94" s="7" t="s">
         <v>17</v>
@@ -6128,14 +6128,14 @@
       <c r="I94" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J94" s="10">
-        <v>100</v>
+      <c r="J94" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K94" s="9">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="L94" s="8">
-        <v>-10</v>
+        <v>0</v>
+      </c>
+      <c r="L94" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M94" s="9">
         <v>0</v>
@@ -6143,19 +6143,19 @@
       <c r="N94" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O94" s="10">
-        <v>100</v>
+      <c r="O94" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P94" s="9">
-        <v>0.23599999999999999</v>
-      </c>
-      <c r="Q94" s="8">
-        <v>-10</v>
+        <v>0</v>
+      </c>
+      <c r="Q94" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
-        <v>41944</v>
+        <v>41974</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>17</v>
@@ -6181,14 +6181,14 @@
       <c r="I95" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J95" s="8">
-        <v>-100</v>
+      <c r="J95" s="10">
+        <v>100</v>
       </c>
       <c r="K95" s="9">
         <v>0.23599999999999999</v>
       </c>
       <c r="L95" s="8">
-        <v>-19.3</v>
+        <v>-10</v>
       </c>
       <c r="M95" s="9">
         <v>0</v>
@@ -6196,19 +6196,19 @@
       <c r="N95" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O95" s="8">
-        <v>-100</v>
+      <c r="O95" s="10">
+        <v>100</v>
       </c>
       <c r="P95" s="9">
         <v>0.23599999999999999</v>
       </c>
       <c r="Q95" s="8">
-        <v>-19.3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
-        <v>41913</v>
+        <v>41944</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>17</v>
@@ -6229,33 +6229,86 @@
         <v>17</v>
       </c>
       <c r="H96" s="9">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I96" s="9" t="s">
         <v>17</v>
       </c>
       <c r="J96" s="8">
-        <v>-71.5</v>
+        <v>-100</v>
       </c>
       <c r="K96" s="9">
         <v>0.23599999999999999</v>
       </c>
-      <c r="L96" s="10">
-        <v>16.600000000000001</v>
+      <c r="L96" s="8">
+        <v>-19.3</v>
       </c>
       <c r="M96" s="9">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="N96" s="9" t="s">
         <v>17</v>
       </c>
       <c r="O96" s="8">
-        <v>-71.5</v>
+        <v>-100</v>
       </c>
       <c r="P96" s="9">
         <v>0.23599999999999999</v>
       </c>
-      <c r="Q96" s="10">
+      <c r="Q96" s="8">
+        <v>-19.3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>41913</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H97" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J97" s="8">
+        <v>-71.5</v>
+      </c>
+      <c r="K97" s="9">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="L97" s="10">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="M97" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="N97" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O97" s="8">
+        <v>-71.5</v>
+      </c>
+      <c r="P97" s="9">
+        <v>0.23599999999999999</v>
+      </c>
+      <c r="Q97" s="10">
         <v>16.600000000000001</v>
       </c>
     </row>
